--- a/astro-site/public/dl/plan-negocio-hamburgueseria/checklist-apertura-hamburgueseria.xlsx
+++ b/astro-site/public/dl/plan-negocio-hamburgueseria/checklist-apertura-hamburgueseria.xlsx
@@ -1804,7 +1804,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Los compuestos polares tienen que quedar por debajo del 25 %, nada se añade al baño y el aceite usado no vuelve a la cocina (Orden de 26 de enero de 1989, arts. 6.3 y 9). La norma no te obliga a tener un medidor: tu APPCC elige tiras, medidor o cambio por frecuencia. Filtra, rellena y anota cada cambio</t>
+          <t>Los compuestos polares tienen que quedar por debajo del 25 %, no se añade al baño nada ajeno al aceite y el usado no vuelve a la cocina (Orden de 26 de enero de 1989, arts. 6.3 y 9). La norma no te obliga a tener un medidor: tu APPCC elige tiras, medidor o cambio por frecuencia. Filtra, rellena y anota cada cambio</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Seis smash (simple, doble, triple, con bacon, con cebolla a la plancha y la de la casa), un pollo crujiente, una vegetal, patatas clásicas y cargadas, tres salsas, tres batidos, refrescos, cerveza de tirador, agua y dos postres, más el menú de doble con patatas y bebida. Una carta de 12 hamburguesas y 6 salsas llena la cámara de pan y de ingredientes que se tiran</t>
+          <t>Seis smash (simple, doble, triple, con bacon, estilo Oklahoma y la de la casa), un pollo crujiente, una vegetal, patatas clásicas y cargadas, batido, postre, el menú de doble con patatas y bebida y el pedido para dos: las 14 filas del escandallo de la calculadora. Aparte, tres salsas, refrescos, cerveza de tirador y agua. Una carta de 12 hamburguesas y 6 salsas llena la cámara de pan y de ingredientes que se tiran</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-hamburgueseria/checklist-apertura-hamburgueseria.xlsx
+++ b/astro-site/public/dl/plan-negocio-hamburgueseria/checklist-apertura-hamburgueseria.xlsx
@@ -1669,7 +1669,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>No se pica carne madurada más de 15 días: Madrid Salud lo dejó escrito en su informe Inf26008 (febrero de 2026) ante una hamburguesería que servía bolas de carne madurada. La «dry aged burger» que vende internet no cabe en un plan que vas a enseñar a un inspector</t>
+          <t>Se pica dentro de los 6 días siguientes al sacrificio (15 si es vacuno deshuesado y envasado al vacío), según el Reglamento 853/2004: una carne madurada semanas queda fuera de plazo, y Madrid Salud lo aplicó así en su informe Inf26008 (febrero de 2026) ante una hamburguesería que servía bolas de carne madurada. La «dry aged burger» que vende internet no cabe en un plan que vas a enseñar a un inspector</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>El batido de leche no es una bebida refrescante: el plan lo lleva al 10 %, pero pide a tu gestoría que lo confirme. El menú que sale del local se desglosa por componentes en el tique: la comida al 10 % y la bebida a su tipo</t>
+          <t>El art. 91 no recoge el batido expresamente: el plan lo lleva al 10 % como bebida de leche; confírmalo con tu gestoría, porque con azúcares o edulcorantes añadidos podría considerarse bebida refrescante (21 %). El menú que sale del local se desglosa por componentes en el tique: la comida al 10 % y la bebida a su tipo</t>
         </is>
       </c>
     </row>
